--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_81_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_81_R9.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2431</v>
+        <v>5.0255</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8477</v>
+        <v>4.6301</v>
       </c>
       <c r="F2" t="n">
         <v>0.3954</v>
@@ -610,10 +610,10 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.861</v>
+        <v>-0.0786</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1949</v>
+        <v>-0.4125</v>
       </c>
       <c r="U2" t="n">
         <v>0.3339</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>I. BAKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3591</v>
+        <v>1.2066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.9883</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8536</v>
+        <v>0.2182</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3482</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0504</v>
+        <v>-0.0048</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3986</v>
+        <v>-0.6993</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9445</v>
+        <v>0.0536</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2318</v>
+        <v>0.0168</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7127</v>
+        <v>0.0368</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4037</v>
+        <v>-0.7577</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2822</v>
+        <v>-0.0216</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6859</v>
+        <v>-0.7361</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3129</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5375</v>
+        <v>-0.1375</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7754</v>
+        <v>0.0481</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
         <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BAKO</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0715</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7524</v>
+        <v>-0.7173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3191</v>
+        <v>1.4839</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-1.3482</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0048</v>
+        <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6993</v>
+        <v>-1.3986</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0536</v>
+        <v>-0.9445</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0168</v>
+        <v>-0.2318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>-0.7127</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7577</v>
+        <v>-0.4037</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0216</v>
+        <v>0.2822</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7361</v>
+        <v>-0.6859</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2245</v>
+        <v>0.7205</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3734</v>
+        <v>0.3148</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1489</v>
+        <v>0.4057</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
         <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6423</v>
+        <v>0.1354</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0423</v>
+        <v>-0.2468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6846</v>
+        <v>0.3821</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2228</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0249</v>
+        <v>0.5179</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9164</v>
+        <v>0.7119</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1085</v>
+        <v>-0.1939</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.595</v>
+        <v>0.0731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1502</v>
+        <v>-0.2036</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4448</v>
+        <v>0.2768</v>
       </c>
       <c r="G6" t="n">
         <v>0.5577</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7332</v>
+        <v>0.2113</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0399</v>
+        <v>-0.3665</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.753</v>
+        <v>-0.6818</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7929</v>
+        <v>0.3154</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0175</v>
+        <v>-2.3885</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1249</v>
+        <v>0.6129</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.1424</v>
+        <v>-3.0014</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.1491</v>
+        <v>-1.0343</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1141</v>
+        <v>0.5419</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.035</v>
+        <v>-1.5762</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8683</v>
+        <v>-1.3542</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2391</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1074</v>
+        <v>-1.4252</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>1.274</v>
+        <v>-0.174</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3961</v>
+        <v>0.244</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1221</v>
+        <v>-0.418</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.117</v>
+        <v>-0.5184</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3705</v>
+        <v>-2.3114</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4875</v>
+        <v>1.7929</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2706</v>
+        <v>-4.0175</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3554</v>
+        <v>0.1249</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6261</v>
+        <v>-4.1424</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5919</v>
+        <v>-3.1491</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.1141</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-3.035</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6787</v>
+        <v>-0.8683</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2714</v>
+        <v>0.2391</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.1074</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4701</v>
+        <v>0.7156</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1098</v>
+        <v>0.8377</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3602</v>
+        <v>-0.1221</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5767</v>
+        <v>-0.757</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6569</v>
+        <v>0.3272</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0801</v>
+        <v>-1.0842</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3885</v>
+        <v>-1.2706</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6129</v>
+        <v>0.3554</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0014</v>
+        <v>-1.6261</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0343</v>
+        <v>-0.5919</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5419</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5762</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3542</v>
+        <v>-0.6787</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2714</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4252</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3842</v>
+        <v>-0.11</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.731</v>
+        <v>-0.1531</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6532</v>
+        <v>0.0431</v>
       </c>
       <c r="V9" t="n">
-        <v>2.428</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>2.428</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.119</v>
+        <v>-1.1349</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7786</v>
+        <v>0.0038</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3404</v>
+        <v>-1.1387</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2176</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4734</v>
+        <v>-0.4894</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1949</v>
+        <v>-0.4125</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2785</v>
+        <v>-0.0769</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3558</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2221</v>
+        <v>-1.7024</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6673</v>
+        <v>-2.282</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4453</v>
+        <v>0.5797</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4744</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5157</v>
+        <v>0.004</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2047</v>
+        <v>0.59</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7204</v>
+        <v>-0.586</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8191</v>
+        <v>-2.5646</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4618</v>
+        <v>-1.9755</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6427</v>
+        <v>-0.5891</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2822</v>
+        <v>-2.2637</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7503</v>
+        <v>0.2391</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5319</v>
+        <v>-2.5027</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2748</v>
+        <v>-1.331</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0109</v>
+        <v>0.168</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7361</v>
+        <v>-1.4991</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0073</v>
+        <v>-0.9326</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2606</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2679</v>
+        <v>-1.0037</v>
       </c>
       <c r="P12" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2311</v>
+        <v>-0.0147</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0272</v>
+        <v>0.5153</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2583</v>
+        <v>-0.53</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1179</v>
+        <v>-3.064</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3608</v>
+        <v>-3.5051</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7571</v>
+        <v>0.4411</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2637</v>
+        <v>-3.2822</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2391</v>
+        <v>-2.7503</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5027</v>
+        <v>-0.5319</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.331</v>
+        <v>-2.2748</v>
       </c>
       <c r="K13" t="n">
-        <v>0.168</v>
+        <v>-3.0109</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4991</v>
+        <v>0.7361</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9326</v>
+        <v>-1.0073</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2606</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0037</v>
+        <v>-1.2679</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.0138</v>
       </c>
       <c r="T13" t="n">
-        <v>0.13</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.698</v>
+        <v>0.0567</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.020900000000001</v>
+        <v>-2.900599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.0944</v>
+        <v>-5.974100000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>3.073500000000001</v>
+        <v>3.0735</v>
       </c>
       <c r="G14" t="n">
         <v>-16.0253</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2694999999999997</v>
+        <v>0.2694999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-16.2947</v>
@@ -1537,7 +1537,7 @@
         <v>-13.7171</v>
       </c>
       <c r="P14" t="n">
-        <v>6.958399999999999</v>
+        <v>6.9584</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.9173</v>
@@ -1546,13 +1546,13 @@
         <v>20.8759</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07919999999999972</v>
+        <v>1.1994</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9663999999999998</v>
+        <v>2.0867</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8871000000000002</v>
+        <v>-0.8872</v>
       </c>
       <c r="V14" t="n">
         <v>4.9666</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3363</v>
+        <v>4.174</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2168</v>
+        <v>3.0989</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1195</v>
+        <v>1.0751</v>
       </c>
       <c r="G15" t="n">
         <v>-0.967</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.695</v>
+        <v>0.5327</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0553</v>
+        <v>-0.0626</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>3.2166</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3283</v>
+        <v>3.048</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4025</v>
+        <v>2.3581</v>
       </c>
       <c r="G16" t="n">
         <v>3.1904</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3725</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1221</v>
+        <v>-0.1138</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2504</v>
+        <v>0.206</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9304</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.869</v>
+        <v>2.7061</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4476</v>
+        <v>2.0938</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4214</v>
+        <v>0.6123</v>
       </c>
       <c r="G17" t="n">
         <v>1.4937</v>
@@ -1780,13 +1780,13 @@
         <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4116</v>
+        <v>0.2486</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6176</v>
+        <v>0.2638</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.206</v>
+        <v>-0.0151</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3558</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4439</v>
+        <v>2.5442</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3695</v>
+        <v>1.0772</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0744</v>
+        <v>1.467</v>
       </c>
       <c r="G18" t="n">
         <v>6.4597</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6241</v>
+        <v>-0.5239</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1123</v>
+        <v>-0.4046</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5118</v>
+        <v>-0.1193</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2406</v>
+        <v>1.8574</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1719</v>
+        <v>-0.1239</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4125</v>
+        <v>1.9814</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0804</v>
+        <v>1.6108</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.767</v>
+        <v>-1.618</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8474</v>
+        <v>3.2288</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1541</v>
+        <v>1.6645</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4887</v>
+        <v>-1.1526</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6428</v>
+        <v>2.817</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9263</v>
+        <v>-0.0537</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7217</v>
+        <v>-0.4655</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2046</v>
+        <v>0.4118</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2324</v>
+        <v>-0.4492</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8338</v>
+        <v>-0.3967</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6014</v>
+        <v>-0.0525</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7572</v>
+        <v>1.0269</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8317</v>
+        <v>-0.6437</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5888</v>
+        <v>1.6705</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6108</v>
+        <v>2.0804</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.618</v>
+        <v>-0.767</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2288</v>
+        <v>2.8474</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6645</v>
+        <v>0.1541</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1526</v>
+        <v>-1.4887</v>
       </c>
       <c r="L20" t="n">
-        <v>2.817</v>
+        <v>1.6428</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0537</v>
+        <v>1.9263</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4655</v>
+        <v>0.7217</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4118</v>
+        <v>1.2046</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5494</v>
+        <v>0.0187</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1044</v>
+        <v>0.362</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.445</v>
+        <v>-0.3433</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2394</v>
+        <v>-1.4585</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.771</v>
+        <v>-2.2777</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5317</v>
+        <v>0.8192</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3482</v>
+        <v>3.0498</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3745</v>
+        <v>0.5571</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9736</v>
+        <v>2.4927</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3732</v>
+        <v>2.8891</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7709</v>
+        <v>0.3396</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6022999999999999</v>
+        <v>2.5495</v>
       </c>
       <c r="M21" t="n">
-        <v>0.025</v>
+        <v>0.1607</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3963</v>
+        <v>0.2175</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3713</v>
+        <v>-0.0568</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>-4.871</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>-5.7988</v>
       </c>
       <c r="R21" t="n">
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5727</v>
+        <v>-0.0316</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8521</v>
+        <v>-0.4402</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2794</v>
+        <v>0.4086</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3469</v>
+        <v>-2.0257</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2777</v>
+        <v>-2.7146</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9308</v>
+        <v>0.6889</v>
       </c>
       <c r="G22" t="n">
-        <v>3.0498</v>
+        <v>-2.3482</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5571</v>
+        <v>-1.3745</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4927</v>
+        <v>-0.9736</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8891</v>
+        <v>-2.3732</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3396</v>
+        <v>-1.7709</v>
       </c>
       <c r="L22" t="n">
-        <v>2.5495</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1607</v>
+        <v>0.025</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2175</v>
+        <v>0.3963</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0568</v>
+        <v>-0.3713</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.871</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.7988</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08</v>
+        <v>0.7863</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4402</v>
+        <v>0.9085</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5201</v>
+        <v>-0.1221</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3821</v>
+        <v>-2.3263</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4464</v>
+        <v>-0.6823</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9357</v>
+        <v>-1.644</v>
       </c>
       <c r="G23" t="n">
         <v>1.523</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0975</v>
+        <v>0.1533</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4208</v>
+        <v>0.1849</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3233</v>
+        <v>-0.0316</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0748</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9862</v>
+        <v>-3.9525</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5347</v>
+        <v>-3.5911</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4515</v>
+        <v>-0.3614</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0674</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3673</v>
+        <v>0.6664</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3576</v>
+        <v>0.586</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0097</v>
+        <v>0.0804</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.0207</v>
+        <v>5.5936</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.073600000000001</v>
+        <v>-3.073400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>7.0944</v>
+        <v>8.6671</v>
       </c>
       <c r="G25" t="n">
         <v>16.0252</v>
@@ -2404,13 +2404,13 @@
         <v>13.9173</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.07910000000000034</v>
+        <v>1.4936</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8872000000000002</v>
+        <v>0.8873</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9665000000000001</v>
+        <v>0.6064000000000002</v>
       </c>
       <c r="V25" t="n">
         <v>-4.9667</v>
